--- a/CO国試data/CO_questions_2020.xlsx
+++ b/CO国試data/CO_questions_2020.xlsx
@@ -542,15 +542,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>視覚情報処理過程の概要</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>3</v>
       </c>
@@ -599,7 +599,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>False</t>
@@ -635,15 +634,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>視覚情報処理過程の概要</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -692,7 +691,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>False</t>
@@ -728,15 +726,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>遺伝</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -785,7 +783,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>False</t>
@@ -821,15 +818,15 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -878,7 +875,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>False</t>
@@ -914,15 +910,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>3</v>
       </c>
@@ -971,7 +967,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>False</t>
@@ -1010,12 +1005,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>3</v>
       </c>
@@ -1064,7 +1059,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>False</t>
@@ -1100,15 +1094,15 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>視能障害のリハビリテーション</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>3</v>
       </c>
@@ -1157,7 +1151,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>False</t>
@@ -1193,15 +1186,15 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>視覚情報処理過程の概要</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -1250,7 +1243,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>False</t>
@@ -1286,15 +1278,15 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>視覚情報処理過程の概要</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>3</v>
       </c>
@@ -1343,7 +1335,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>False</t>
@@ -1379,15 +1370,15 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>3</v>
       </c>
@@ -1436,7 +1427,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>True</t>
@@ -1472,15 +1462,15 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>視覚情報処理過程の概要</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>3</v>
       </c>
@@ -1529,7 +1519,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>False</t>
@@ -1565,15 +1554,15 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>2</v>
       </c>
@@ -1622,7 +1611,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>False</t>
@@ -1658,15 +1646,15 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>3</v>
       </c>
@@ -1715,7 +1703,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>False</t>
@@ -1751,15 +1738,15 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>4</v>
       </c>
@@ -1808,7 +1795,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>False</t>
@@ -1844,15 +1830,15 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>3</v>
       </c>
@@ -1901,7 +1887,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>False</t>
@@ -1937,15 +1922,15 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>3</v>
       </c>
@@ -1994,7 +1979,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>False</t>
@@ -2030,15 +2014,15 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>3</v>
       </c>
@@ -2087,7 +2071,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>False</t>
@@ -2123,15 +2106,15 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>4</v>
       </c>
@@ -2180,7 +2163,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>False</t>
@@ -2216,15 +2198,15 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>3</v>
       </c>
@@ -2273,7 +2255,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>False</t>
@@ -2309,15 +2290,15 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>4</v>
       </c>
@@ -2407,15 +2388,15 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>3</v>
       </c>
@@ -2464,7 +2445,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>True</t>
@@ -2500,15 +2480,15 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>4</v>
       </c>
@@ -2557,7 +2537,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>False</t>
@@ -2593,15 +2572,15 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
+          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>視能障害のリハビリテーション</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>3</v>
       </c>
@@ -2650,7 +2629,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>False</t>
@@ -2686,15 +2664,15 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>2</v>
       </c>
@@ -2743,7 +2721,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>False</t>
@@ -2779,15 +2756,15 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>3</v>
       </c>
@@ -2836,7 +2813,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>False</t>
@@ -2872,15 +2848,15 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>3</v>
       </c>
@@ -2929,7 +2905,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>False</t>
@@ -2965,15 +2940,15 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>3</v>
       </c>
@@ -3022,7 +2997,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>False</t>
@@ -3061,12 +3035,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>1</v>
       </c>
@@ -3115,7 +3089,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>False</t>
@@ -3151,15 +3124,15 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>3</v>
       </c>
@@ -3208,7 +3181,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>True</t>
@@ -3244,15 +3216,15 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>4</v>
       </c>
@@ -3302,7 +3274,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
           <t>False</t>
@@ -3338,15 +3309,15 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>3</v>
       </c>
@@ -3395,7 +3366,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
           <t>True</t>
@@ -3431,15 +3401,15 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>2</v>
       </c>
@@ -3488,7 +3458,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
           <t>False</t>
@@ -3524,15 +3493,15 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>4</v>
       </c>
@@ -3581,7 +3550,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
           <t>True</t>
@@ -3617,15 +3585,15 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>3</v>
       </c>
@@ -3675,7 +3643,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
           <t>False</t>
@@ -3711,15 +3678,15 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>4</v>
       </c>
@@ -3769,7 +3736,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
           <t>True</t>
@@ -3805,15 +3771,15 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>3</v>
       </c>
@@ -3862,7 +3828,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
           <t>False</t>
@@ -3898,15 +3863,15 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>2</v>
       </c>
@@ -3955,7 +3920,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
           <t>False</t>
@@ -3991,15 +3955,15 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>3</v>
       </c>
@@ -4048,7 +4012,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
           <t>True</t>
@@ -4084,15 +4047,15 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>3</v>
       </c>
@@ -4141,7 +4104,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
           <t>False</t>
@@ -4177,15 +4139,15 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>2</v>
       </c>
@@ -4234,7 +4196,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
           <t>False</t>
@@ -4270,15 +4231,15 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>2</v>
       </c>
@@ -4327,7 +4288,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
           <t>False</t>
@@ -4363,15 +4323,15 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>3</v>
       </c>
@@ -4420,7 +4380,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
           <t>True</t>
@@ -4456,15 +4415,15 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>2</v>
       </c>
@@ -4513,7 +4472,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
           <t>False</t>
@@ -4552,12 +4510,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>公衆衛生学</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>2</v>
       </c>
@@ -4606,7 +4564,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
           <t>False</t>
@@ -4642,15 +4599,15 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>3</v>
       </c>
@@ -4699,7 +4656,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
           <t>True</t>
@@ -4735,15 +4691,15 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>2</v>
       </c>
@@ -4792,7 +4748,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
           <t>False</t>
@@ -4828,15 +4783,15 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>3</v>
       </c>
@@ -4885,7 +4840,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
           <t>False</t>
@@ -4921,15 +4875,15 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>2</v>
       </c>
@@ -4978,7 +4932,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
           <t>True</t>
@@ -5017,12 +4970,12 @@
           <t>疾病と障害の成り立ち及び回復過程の促進</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>疾患の診断と治療</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>3</v>
       </c>
@@ -5071,7 +5024,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
           <t>False</t>
@@ -5107,15 +5059,15 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>4</v>
       </c>
@@ -5164,7 +5116,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
           <t>True</t>
@@ -5200,15 +5151,15 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>3</v>
       </c>
@@ -5257,7 +5208,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
           <t>False</t>
@@ -5296,12 +5246,12 @@
           <t>疾病と障害の成り立ち及び回復過程の促進</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>疾患の診断と治療</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>5</v>
       </c>
@@ -5350,7 +5300,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
           <t>True</t>
@@ -5386,15 +5335,15 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>4</v>
       </c>
@@ -5443,7 +5392,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
           <t>False</t>
@@ -5479,15 +5427,15 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>3</v>
       </c>
@@ -5536,7 +5484,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
           <t>False</t>
@@ -5572,15 +5519,15 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>4</v>
       </c>
@@ -5629,7 +5576,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
           <t>False</t>
@@ -5665,15 +5611,15 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>3</v>
       </c>
@@ -5722,7 +5668,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
           <t>False</t>
@@ -5758,15 +5703,15 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>3</v>
       </c>
@@ -5815,7 +5760,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
           <t>False</t>
@@ -5851,15 +5795,15 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>3</v>
       </c>
@@ -5908,7 +5852,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
           <t>True</t>
@@ -5944,15 +5887,15 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>4</v>
       </c>
@@ -6001,7 +5944,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
           <t>False</t>
@@ -6037,15 +5979,15 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>4</v>
       </c>
@@ -6094,7 +6036,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
           <t>True</t>
@@ -6130,15 +6071,15 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>3</v>
       </c>
@@ -6187,7 +6128,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
           <t>True</t>
@@ -6223,15 +6163,15 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>3</v>
       </c>
@@ -6280,7 +6220,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
           <t>True</t>
@@ -6316,15 +6255,15 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>4</v>
       </c>
@@ -6373,7 +6312,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
           <t>False</t>
@@ -6409,15 +6347,15 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
         <v>3</v>
       </c>
@@ -6466,7 +6404,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
           <t>False</t>
@@ -6502,15 +6439,15 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>4</v>
       </c>
@@ -6603,12 +6540,12 @@
           <t>疾病と障害の成り立ち及び回復過程の促進</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>疾患の診断と治療</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
         <v>5</v>
       </c>
@@ -6698,15 +6635,15 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
         <v>4</v>
       </c>
@@ -6756,7 +6693,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
           <t>False</t>
@@ -6792,15 +6728,15 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>4</v>
       </c>
@@ -6890,15 +6826,15 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
         <v>5</v>
       </c>
@@ -6988,15 +6924,15 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>3</v>
       </c>
@@ -7086,15 +7022,15 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>5</v>
       </c>
@@ -7187,12 +7123,12 @@
           <t>疾病と障害の成り立ち及び回復過程の促進</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>疾患の診断と治療</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>3</v>
       </c>
@@ -7282,15 +7218,15 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>5</v>
       </c>
@@ -7380,15 +7316,15 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>4</v>
       </c>
@@ -7438,7 +7374,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
           <t>True</t>
@@ -7474,15 +7409,15 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
         <v>5</v>
       </c>
@@ -7572,15 +7507,15 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>視覚情報処理過程の概要</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
         <v>1</v>
       </c>
@@ -7629,7 +7564,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
           <t>False</t>
@@ -7665,15 +7599,15 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>心臓、血管</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>2</v>
       </c>
@@ -7722,7 +7656,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
           <t>False</t>
@@ -7758,15 +7691,15 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
         <v>2</v>
       </c>
@@ -7815,7 +7748,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
           <t>False</t>
@@ -7851,15 +7783,15 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
         <v>2</v>
       </c>
@@ -7908,7 +7840,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
           <t>False</t>
@@ -7944,15 +7875,15 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>2</v>
       </c>
@@ -8001,7 +7932,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
           <t>False</t>
@@ -8040,12 +7970,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
         <v>3</v>
       </c>
@@ -8094,7 +8024,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
           <t>True</t>
@@ -8130,15 +8059,15 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>視覚情報処理過程の概要</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
         <v>2</v>
       </c>
@@ -8187,7 +8116,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
           <t>False</t>
@@ -8226,12 +8154,12 @@
           <t>疾病と障害の成り立ち及び回復過程の促進</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>病態の基礎</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
         <v>1</v>
       </c>
@@ -8280,7 +8208,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
           <t>False</t>
@@ -8316,15 +8243,15 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>脳・神経</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
         <v>2</v>
       </c>
@@ -8373,7 +8300,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
           <t>False</t>
@@ -8409,15 +8335,15 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
         <v>2</v>
       </c>
@@ -8466,7 +8392,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
           <t>False</t>
@@ -8502,15 +8427,15 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
         <v>2</v>
       </c>
@@ -8559,7 +8484,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
           <t>False</t>
@@ -8595,15 +8519,15 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
         <v>2</v>
       </c>
@@ -8652,7 +8576,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
           <t>False</t>
@@ -8688,15 +8611,15 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
         <v>4</v>
       </c>
@@ -8745,7 +8668,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
           <t>False</t>
@@ -8781,15 +8703,15 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
         <v>3</v>
       </c>
@@ -8838,7 +8760,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
           <t>False</t>
@@ -8874,15 +8795,15 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>視能検査法と検査機器の基礎</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>3</v>
       </c>
@@ -8931,7 +8852,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
           <t>False</t>
@@ -8967,15 +8887,15 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>4</v>
       </c>
@@ -9065,15 +8985,15 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
         <v>4</v>
       </c>
@@ -9163,15 +9083,15 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
         <v>3</v>
       </c>
@@ -9220,7 +9140,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
           <t>True</t>
@@ -9256,15 +9175,15 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
         <v>2</v>
       </c>
@@ -9313,7 +9232,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
           <t>False</t>
@@ -9352,12 +9270,12 @@
           <t>疾病と障害の成り立ち及び回復過程の促進</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>疾患の診断と治療</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
         <v>2</v>
       </c>
@@ -9406,7 +9324,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
           <t>False</t>
@@ -9442,15 +9359,15 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
         <v>4</v>
       </c>
@@ -9540,15 +9457,15 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>3</v>
       </c>
@@ -9641,12 +9558,12 @@
           <t>疾病と障害の成り立ち及び回復過程の促進</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>疾患の診断と治療</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>1</v>
       </c>
@@ -9695,7 +9612,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
           <t>False</t>
@@ -9731,15 +9647,15 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>2</v>
       </c>
@@ -9788,7 +9704,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
           <t>False</t>
@@ -9824,15 +9739,15 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>視覚情報処理過程の概要</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>2</v>
       </c>
@@ -9881,7 +9796,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
           <t>False</t>
@@ -9920,12 +9834,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
         <v>1</v>
       </c>
@@ -9974,7 +9888,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
           <t>False</t>
@@ -10010,15 +9923,15 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>3</v>
       </c>
@@ -10067,7 +9980,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
           <t>True</t>
@@ -10103,15 +10015,15 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
         <v>3</v>
       </c>
@@ -10160,7 +10072,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
           <t>False</t>
@@ -10196,15 +10107,15 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>3</v>
       </c>
@@ -10253,7 +10164,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
           <t>True</t>
@@ -10289,15 +10199,15 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
         <is>
           <t>心臓、血管</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>3</v>
       </c>
@@ -10346,7 +10256,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr">
         <is>
           <t>False</t>
@@ -10382,15 +10291,15 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>3</v>
       </c>
@@ -10439,7 +10348,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
           <t>False</t>
@@ -10475,15 +10383,15 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>3</v>
       </c>
@@ -10573,15 +10481,15 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
         <v>3</v>
       </c>
@@ -10630,7 +10538,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
           <t>False</t>
@@ -10669,12 +10576,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr">
+      <c r="F110" t="inlineStr">
         <is>
           <t>公衆衛生学</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>2</v>
       </c>
@@ -10723,7 +10630,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
           <t>False</t>
@@ -10762,12 +10668,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
+      <c r="F111" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>1</v>
       </c>
@@ -10816,7 +10722,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
           <t>False</t>
@@ -10855,12 +10760,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
+      <c r="F112" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>1</v>
       </c>
@@ -10909,7 +10814,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr">
         <is>
           <t>False</t>
@@ -10945,15 +10849,15 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
         <v>2</v>
       </c>
@@ -11002,7 +10906,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr">
         <is>
           <t>False</t>
@@ -11038,15 +10941,15 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
         <v>1</v>
       </c>
@@ -11095,7 +10998,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr">
         <is>
           <t>False</t>
@@ -11131,15 +11033,15 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
         <v>3</v>
       </c>
@@ -11188,7 +11090,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr">
         <is>
           <t>False</t>
@@ -11224,15 +11125,15 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
         <v>2</v>
       </c>
@@ -11281,7 +11182,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr">
         <is>
           <t>False</t>
@@ -11317,15 +11217,15 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
         <v>2</v>
       </c>
@@ -11374,7 +11274,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr">
         <is>
           <t>True</t>
@@ -11410,15 +11309,15 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
         <v>3</v>
       </c>
@@ -11467,7 +11366,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
           <t>True</t>
@@ -11503,15 +11401,15 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
         <v>2</v>
       </c>
@@ -11560,7 +11458,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
           <t>True</t>
@@ -11596,15 +11493,15 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
         <v>2</v>
       </c>
@@ -11653,7 +11550,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
           <t>True</t>
@@ -11689,15 +11585,15 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
         <is>
           <t>脳・神経</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
         <v>2</v>
       </c>
@@ -11746,7 +11642,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
           <t>False</t>
@@ -11782,15 +11677,15 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
         <v>2</v>
       </c>
@@ -11839,7 +11734,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr">
         <is>
           <t>False</t>
@@ -11875,15 +11769,15 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
         <v>2</v>
       </c>
@@ -11932,7 +11826,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
           <t>True</t>
@@ -11968,15 +11861,15 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
         <v>2</v>
       </c>
@@ -12025,7 +11918,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
           <t>False</t>
@@ -12061,15 +11953,15 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
         <v>2</v>
       </c>
@@ -12118,7 +12010,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
           <t>False</t>
@@ -12154,15 +12045,15 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
         <v>4</v>
       </c>
@@ -12211,7 +12102,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
           <t>True</t>
@@ -12247,15 +12137,15 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
         <v>3</v>
       </c>
@@ -12304,7 +12194,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
           <t>False</t>
@@ -12340,15 +12229,15 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
         <is>
           <t>心身の成長・発達、加齢</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
         <v>3</v>
       </c>
@@ -12397,7 +12286,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
           <t>False</t>
@@ -12433,15 +12321,15 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
         <v>4</v>
       </c>
@@ -12490,7 +12378,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
           <t>True</t>
@@ -12526,15 +12413,15 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
         <v>3</v>
       </c>
@@ -12583,7 +12470,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
           <t>False</t>
@@ -12619,15 +12505,15 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
         <v>3</v>
       </c>
@@ -12676,7 +12562,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
           <t>False</t>
@@ -12712,15 +12597,15 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
         <v>2</v>
       </c>
@@ -12769,7 +12654,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr">
         <is>
           <t>True</t>
@@ -12805,15 +12689,15 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
         <v>2</v>
       </c>
@@ -12862,7 +12746,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr">
         <is>
           <t>False</t>
@@ -12898,15 +12781,15 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
         <v>3</v>
       </c>
@@ -12955,7 +12838,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
           <t>True</t>
@@ -12991,15 +12873,15 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
         <v>4</v>
       </c>
@@ -13048,7 +12930,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
           <t>True</t>
@@ -13084,15 +12965,15 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
         <v>3</v>
       </c>
@@ -13141,7 +13022,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr">
         <is>
           <t>False</t>
@@ -13177,15 +13057,15 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
         <v>3</v>
       </c>
@@ -13234,7 +13114,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
           <t>False</t>
@@ -13270,15 +13149,15 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
         <v>4</v>
       </c>
@@ -13328,7 +13207,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
           <t>False</t>
@@ -13367,12 +13245,12 @@
           <t>疾病と障害の成り立ち及び回復過程の促進</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>疾患の診断と治療</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
         <v>3</v>
       </c>
@@ -13421,7 +13299,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
           <t>False</t>
@@ -13457,15 +13334,15 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
         <v>3</v>
       </c>
@@ -13514,7 +13391,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
           <t>True</t>
@@ -13550,15 +13426,15 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
         <v>4</v>
       </c>
@@ -13607,7 +13483,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
           <t>True</t>
@@ -13643,15 +13518,15 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
         <v>4</v>
       </c>
@@ -13701,7 +13576,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr">
         <is>
           <t>False</t>
@@ -13737,15 +13611,15 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
         <v>3</v>
       </c>
@@ -13835,15 +13709,15 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
         <v>4</v>
       </c>
@@ -13933,15 +13807,15 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
         <v>4</v>
       </c>
@@ -13991,7 +13865,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr">
         <is>
           <t>True</t>
@@ -14027,15 +13900,15 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
         <v>3</v>
       </c>
@@ -14125,15 +13998,15 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
         <v>3</v>
       </c>
@@ -14223,15 +14096,15 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
         <v>4</v>
       </c>
@@ -14321,15 +14194,15 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
         <v>3</v>
       </c>
@@ -14419,15 +14292,15 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
         <v>3</v>
       </c>
@@ -14517,15 +14390,15 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
         <v>5</v>
       </c>

--- a/CO国試data/CO_questions_2020.xlsx
+++ b/CO国試data/CO_questions_2020.xlsx
@@ -542,12 +542,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視覚情報処理過程の概要</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>視覚情報処理過程の概要</t>
+          <t>視神経</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -634,12 +634,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視覚情報処理過程の概要</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>視覚情報処理過程の概要</t>
+          <t>眼の自律神経系</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -726,12 +726,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>遺伝</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>遺伝</t>
+          <t>遺伝子</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -818,12 +818,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -910,12 +910,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>保健、医療、福祉、介護の推進</t>
+          <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能障害のリハビリテーション</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>視能障害のリハビリテーション</t>
+          <t>ロービジョン</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視覚情報処理過程の概要</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>視覚情報処理過程の概要</t>
+          <t>眼球</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視覚情報処理過程の概要</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>視覚情報処理過程の概要</t>
+          <t>眼球</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視覚情報処理過程の概要</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>視覚情報処理過程の概要</t>
+          <t>眼球</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>両眼視</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1830,12 +1830,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2014,12 +2014,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2198,12 +2198,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2290,12 +2290,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2388,12 +2388,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2480,12 +2480,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>定義</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能障害のリハビリテーション</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -2756,12 +2756,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>輻湊検査</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -2848,12 +2848,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -2940,12 +2940,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼底検査</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3032,12 +3032,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3124,12 +3124,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3216,12 +3216,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3309,12 +3309,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3401,12 +3401,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>両眼視機能検査(網膜対応検</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -3493,12 +3493,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3585,12 +3585,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -3678,12 +3678,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -3771,12 +3771,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>中心フリッカ検査</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>隅角検査</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -3955,12 +3955,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>屈折検査</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4139,12 +4139,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>強膜</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4231,12 +4231,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>水晶体</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>緑内障</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -4415,12 +4415,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼外傷</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -4507,12 +4507,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>公衆衛生学</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>公衆衛生学</t>
+          <t>公衆衛生総論</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>涙液検査</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -4691,12 +4691,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -4783,12 +4783,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>小児視能特性</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -4875,12 +4875,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼窩</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
+          <t>疾患の診断と治療</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>疾患の診断と治療</t>
+          <t>脳、神経系疾患</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -5059,12 +5059,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -5151,12 +5151,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5243,12 +5243,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
+          <t>疾患の診断と治療</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>疾患の診断と治療</t>
+          <t>脳、神経系疾患</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -5335,12 +5335,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -5611,12 +5611,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -5703,12 +5703,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -5795,12 +5795,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -5887,12 +5887,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -5979,12 +5979,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -6071,12 +6071,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -6163,12 +6163,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -6255,12 +6255,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -6347,12 +6347,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -6537,12 +6537,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
+          <t>疾患の診断と治療</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>疾患の診断と治療</t>
+          <t>脳、神経系疾患</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -6635,12 +6635,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -6728,12 +6728,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -6826,12 +6826,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -6924,12 +6924,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>瞳孔</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -7022,12 +7022,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
+          <t>疾患の診断と治療</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>疾患の診断と治療</t>
+          <t>脳、神経系疾患</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>両眼視機能訓練</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -7316,12 +7316,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -7409,12 +7409,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>定義</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -7507,12 +7507,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視覚情報処理過程の概要</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>視覚情報処理過程の概要</t>
+          <t>眼球</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -7599,12 +7599,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>心臓、血管</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>心臓、血管</t>
+          <t>心臓、血管の構造と機能</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -7691,12 +7691,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>薬物の副作用</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -7783,12 +7783,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼球運動</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -7875,12 +7875,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>両眼視機能検査(網膜対応検</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -7967,12 +7967,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>視能訓練士の倫理</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視覚情報処理過程の概要</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>視覚情報処理過程の概要</t>
+          <t>眼球</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -8151,12 +8151,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
+          <t>病態の基礎</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>病態の基礎</t>
+          <t>疾病の原因</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>脳・神経</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>脳・神経</t>
+          <t>中枢神経の構造と機能</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -8335,12 +8335,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -8611,12 +8611,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -8703,12 +8703,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -8795,12 +8795,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視能検査法と検査機器の基礎</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>視能検査法と検査機器の基礎</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -8887,12 +8887,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -8985,12 +8985,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -9083,12 +9083,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -9175,12 +9175,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -9267,12 +9267,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
+          <t>疾患の診断と治療</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>疾患の診断と治療</t>
+          <t>脳、神経系疾患</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -9359,12 +9359,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -9457,12 +9457,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -9555,12 +9555,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
+          <t>疾患の診断と治療</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>疾患の診断と治療</t>
+          <t>脳、神経系疾患</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -9647,12 +9647,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -9739,12 +9739,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視覚情報処理過程の概要</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>視覚情報処理過程の概要</t>
+          <t>瞳孔反応</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -9831,12 +9831,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -9923,12 +9923,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -10015,12 +10015,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>前眼部、透光体検査</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -10107,12 +10107,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>瞳孔</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
@@ -10199,12 +10199,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>心臓、血管</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>心臓、血管</t>
+          <t>心臓、血管の構造と機能</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -10291,12 +10291,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>隅角検査</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -10481,12 +10481,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼鏡、コンタクトレンズ検査</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
@@ -10573,12 +10573,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>公衆衛生学</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>公衆衛生学</t>
+          <t>公衆衛生総論</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
@@ -10665,12 +10665,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -10757,12 +10757,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -10849,12 +10849,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -10941,12 +10941,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>屈折検査</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
@@ -11033,12 +11033,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
@@ -11125,12 +11125,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>網膜</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
@@ -11217,12 +11217,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>硝子体</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -11309,12 +11309,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>ぶどう膜</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
@@ -11493,12 +11493,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>硝子体</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
@@ -11585,12 +11585,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>脳・神経</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>脳・神経</t>
+          <t>中枢神経の構造と機能</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
@@ -11677,12 +11677,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>緑内障</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>角膜</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
@@ -11861,12 +11861,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>結膜</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
@@ -11953,12 +11953,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
@@ -12045,12 +12045,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
@@ -12137,12 +12137,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
@@ -12229,12 +12229,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>心身の成長・発達、加齢</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>心身の成長・発達、加齢</t>
+          <t>加齢、老化</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
@@ -12321,12 +12321,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>定義</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
@@ -12413,12 +12413,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
@@ -12505,12 +12505,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>屈折検査</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
@@ -12597,12 +12597,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>定義</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
@@ -12689,12 +12689,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
@@ -12781,12 +12781,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
@@ -12965,12 +12965,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
@@ -13057,12 +13057,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
@@ -13149,12 +13149,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
@@ -13242,12 +13242,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
+          <t>疾患の診断と治療</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>疾患の診断と治療</t>
+          <t>脳、神経系疾患</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
@@ -13334,12 +13334,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
@@ -13426,12 +13426,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
@@ -13518,12 +13518,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
@@ -13611,12 +13611,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>瞳孔</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
@@ -13709,12 +13709,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼位検査</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -13807,12 +13807,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
@@ -13900,12 +13900,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G146" t="inlineStr"/>
@@ -13998,12 +13998,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>全身疾患と眼</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
@@ -14096,12 +14096,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
@@ -14194,12 +14194,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>角膜</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
@@ -14292,12 +14292,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
@@ -14390,12 +14390,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G151" t="inlineStr"/>

--- a/CO国試data/CO_questions_2020.xlsx
+++ b/CO国試data/CO_questions_2020.xlsx
@@ -550,7 +550,6 @@
           <t>視神経</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>3</v>
       </c>
@@ -642,7 +641,11 @@
           <t>眼の自律神経系</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>副交感神経</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -734,7 +737,11 @@
           <t>遺伝子</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>基本構造と機能</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -826,7 +833,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -918,7 +924,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H6" t="n">
         <v>3</v>
       </c>
@@ -1010,7 +1020,6 @@
           <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>3</v>
       </c>
@@ -1102,7 +1111,6 @@
           <t>ロービジョン</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>3</v>
       </c>
@@ -1194,7 +1202,6 @@
           <t>眼球</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -1286,7 +1293,6 @@
           <t>眼球</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>3</v>
       </c>
@@ -1378,7 +1384,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>3</v>
       </c>
@@ -1470,7 +1475,6 @@
           <t>眼球</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>3</v>
       </c>
@@ -1562,7 +1566,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>2</v>
       </c>
@@ -1654,7 +1657,11 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>交感神経薬</t>
+        </is>
+      </c>
       <c r="H14" t="n">
         <v>3</v>
       </c>
@@ -1746,7 +1753,11 @@
           <t>両眼視</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Panumの融像感覚圏</t>
+        </is>
+      </c>
       <c r="H15" t="n">
         <v>4</v>
       </c>
@@ -1838,7 +1849,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>3</v>
       </c>
@@ -1930,7 +1940,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>プリズム</t>
+        </is>
+      </c>
       <c r="H17" t="n">
         <v>3</v>
       </c>
@@ -2022,7 +2036,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>近視</t>
+        </is>
+      </c>
       <c r="H18" t="n">
         <v>3</v>
       </c>
@@ -2114,7 +2132,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>4</v>
       </c>
@@ -2206,7 +2223,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>コンタクトレンズ</t>
+        </is>
+      </c>
       <c r="H20" t="n">
         <v>3</v>
       </c>
@@ -2298,7 +2319,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>4</v>
       </c>
@@ -2396,7 +2421,11 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>外眼筋の単独作用</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>3</v>
       </c>
@@ -2488,7 +2517,6 @@
           <t>定義</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>4</v>
       </c>
@@ -2580,7 +2608,6 @@
           <t>視能障害のリハビリテーション</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>3</v>
       </c>
@@ -2672,7 +2699,11 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>乳幼児視力検査（PL法を含む）</t>
+        </is>
+      </c>
       <c r="H25" t="n">
         <v>2</v>
       </c>
@@ -2764,7 +2795,6 @@
           <t>輻湊検査</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>3</v>
       </c>
@@ -2856,7 +2886,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>視覚の成り立ち</t>
+        </is>
+      </c>
       <c r="H27" t="n">
         <v>3</v>
       </c>
@@ -2948,7 +2982,6 @@
           <t>眼底検査</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>3</v>
       </c>
@@ -3040,7 +3073,11 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>インシデント、アクシデントとレポート</t>
+        </is>
+      </c>
       <c r="H29" t="n">
         <v>1</v>
       </c>
@@ -3132,7 +3169,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>3</v>
       </c>
@@ -3224,7 +3260,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H31" t="n">
         <v>4</v>
       </c>
@@ -3317,7 +3357,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>視覚の成り立ち</t>
+        </is>
+      </c>
       <c r="H32" t="n">
         <v>3</v>
       </c>
@@ -3409,7 +3453,11 @@
           <t>両眼視機能検査(網膜対応検</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>プリズムを用いた検査</t>
+        </is>
+      </c>
       <c r="H33" t="n">
         <v>2</v>
       </c>
@@ -3501,7 +3549,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>4</v>
       </c>
@@ -3593,7 +3640,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>3</v>
       </c>
@@ -3686,7 +3732,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>4</v>
       </c>
@@ -3779,7 +3824,11 @@
           <t>中心フリッカ検査</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>限界フリッカ値〈CFF〉</t>
+        </is>
+      </c>
       <c r="H37" t="n">
         <v>3</v>
       </c>
@@ -3871,7 +3920,6 @@
           <t>隅角検査</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>2</v>
       </c>
@@ -3963,7 +4011,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>視神経症</t>
+        </is>
+      </c>
       <c r="H39" t="n">
         <v>3</v>
       </c>
@@ -4055,7 +4107,11 @@
           <t>屈折検査</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>他覚的屈折検査（波面収差解析を含む）</t>
+        </is>
+      </c>
       <c r="H40" t="n">
         <v>3</v>
       </c>
@@ -4147,7 +4203,11 @@
           <t>強膜</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>強膜炎</t>
+        </is>
+      </c>
       <c r="H41" t="n">
         <v>2</v>
       </c>
@@ -4239,7 +4299,11 @@
           <t>水晶体</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>白内障</t>
+        </is>
+      </c>
       <c r="H42" t="n">
         <v>2</v>
       </c>
@@ -4331,7 +4395,11 @@
           <t>緑内障</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>正常眼圧緑内障</t>
+        </is>
+      </c>
       <c r="H43" t="n">
         <v>3</v>
       </c>
@@ -4423,7 +4491,6 @@
           <t>眼外傷</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>2</v>
       </c>
@@ -4515,7 +4582,6 @@
           <t>公衆衛生総論</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>2</v>
       </c>
@@ -4607,7 +4673,11 @@
           <t>涙液検査</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>生体染色検査</t>
+        </is>
+      </c>
       <c r="H46" t="n">
         <v>3</v>
       </c>
@@ -4699,7 +4769,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>形態覚遮断弱視</t>
+        </is>
+      </c>
       <c r="H47" t="n">
         <v>2</v>
       </c>
@@ -4791,7 +4865,6 @@
           <t>小児視能特性</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>3</v>
       </c>
@@ -4883,7 +4956,11 @@
           <t>眼窩</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>眼球突出、陥凹</t>
+        </is>
+      </c>
       <c r="H49" t="n">
         <v>2</v>
       </c>
@@ -4975,7 +5052,6 @@
           <t>脳、神経系疾患</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>3</v>
       </c>
@@ -5067,7 +5143,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>4</v>
       </c>
@@ -5159,7 +5234,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>交代性上斜位</t>
+        </is>
+      </c>
       <c r="H52" t="n">
         <v>3</v>
       </c>
@@ -5251,7 +5330,6 @@
           <t>脳、神経系疾患</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>5</v>
       </c>
@@ -5343,7 +5421,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>4</v>
       </c>
@@ -5435,7 +5512,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>形態覚遮断弱視</t>
+        </is>
+      </c>
       <c r="H55" t="n">
         <v>3</v>
       </c>
@@ -5527,7 +5608,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>屈折矯正</t>
+        </is>
+      </c>
       <c r="H56" t="n">
         <v>4</v>
       </c>
@@ -5619,7 +5704,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>屈折矯正</t>
+        </is>
+      </c>
       <c r="H57" t="n">
         <v>3</v>
       </c>
@@ -5711,7 +5800,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>形態覚遮断弱視</t>
+        </is>
+      </c>
       <c r="H58" t="n">
         <v>3</v>
       </c>
@@ -5803,7 +5896,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>ペナリゼーション</t>
+        </is>
+      </c>
       <c r="H59" t="n">
         <v>3</v>
       </c>
@@ -5895,7 +5992,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>屈折矯正</t>
+        </is>
+      </c>
       <c r="H60" t="n">
         <v>4</v>
       </c>
@@ -5987,7 +6088,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H61" t="n">
         <v>4</v>
       </c>
@@ -6079,7 +6184,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>3</v>
       </c>
@@ -6171,7 +6275,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>3</v>
       </c>
@@ -6263,7 +6366,11 @@
           <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>測定法</t>
+        </is>
+      </c>
       <c r="H64" t="n">
         <v>4</v>
       </c>
@@ -6355,7 +6462,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>斜視特殊型</t>
+        </is>
+      </c>
       <c r="H65" t="n">
         <v>3</v>
       </c>
@@ -6447,7 +6558,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>4</v>
       </c>
@@ -6545,7 +6655,6 @@
           <t>脳、神経系疾患</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
         <v>5</v>
       </c>
@@ -6643,7 +6752,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>眼鏡レンズ</t>
+        </is>
+      </c>
       <c r="H68" t="n">
         <v>4</v>
       </c>
@@ -6736,7 +6849,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>視覚の成り立ち</t>
+        </is>
+      </c>
       <c r="H69" t="n">
         <v>4</v>
       </c>
@@ -6834,7 +6951,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>うっ血乳頭</t>
+        </is>
+      </c>
       <c r="H70" t="n">
         <v>5</v>
       </c>
@@ -6932,7 +7053,6 @@
           <t>瞳孔</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>3</v>
       </c>
@@ -7030,7 +7150,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>屈折矯正</t>
+        </is>
+      </c>
       <c r="H72" t="n">
         <v>5</v>
       </c>
@@ -7128,7 +7252,6 @@
           <t>脳、神経系疾患</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>3</v>
       </c>
@@ -7226,7 +7349,6 @@
           <t>両眼視機能訓練</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>5</v>
       </c>
@@ -7324,7 +7446,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>プリズム</t>
+        </is>
+      </c>
       <c r="H75" t="n">
         <v>4</v>
       </c>
@@ -7417,7 +7543,6 @@
           <t>定義</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
         <v>5</v>
       </c>
@@ -7515,7 +7640,11 @@
           <t>眼球</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>ぶどう膜（虹彩、毛様体、脈絡膜）</t>
+        </is>
+      </c>
       <c r="H77" t="n">
         <v>1</v>
       </c>
@@ -7607,7 +7736,6 @@
           <t>心臓、血管の構造と機能</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>2</v>
       </c>
@@ -7699,7 +7827,11 @@
           <t>薬物の副作用</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>眼科で用いられる薬物の副作用</t>
+        </is>
+      </c>
       <c r="H79" t="n">
         <v>2</v>
       </c>
@@ -7791,7 +7923,11 @@
           <t>眼球運動</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>神経筋接合部障害</t>
+        </is>
+      </c>
       <c r="H80" t="n">
         <v>2</v>
       </c>
@@ -7883,7 +8019,11 @@
           <t>両眼視機能検査(網膜対応検</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Bagolini線条検査</t>
+        </is>
+      </c>
       <c r="H81" t="n">
         <v>2</v>
       </c>
@@ -7975,7 +8115,11 @@
           <t>視能訓練士の倫理</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>守秘義務</t>
+        </is>
+      </c>
       <c r="H82" t="n">
         <v>3</v>
       </c>
@@ -8067,7 +8211,11 @@
           <t>眼球</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>角膜</t>
+        </is>
+      </c>
       <c r="H83" t="n">
         <v>2</v>
       </c>
@@ -8159,7 +8307,6 @@
           <t>疾病の原因</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
         <v>1</v>
       </c>
@@ -8251,7 +8398,6 @@
           <t>中枢神経の構造と機能</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
         <v>2</v>
       </c>
@@ -8343,7 +8489,11 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>点眼薬</t>
+        </is>
+      </c>
       <c r="H86" t="n">
         <v>2</v>
       </c>
@@ -8435,7 +8585,11 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>副交感神経薬</t>
+        </is>
+      </c>
       <c r="H87" t="n">
         <v>2</v>
       </c>
@@ -8527,7 +8681,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>プリズム</t>
+        </is>
+      </c>
       <c r="H88" t="n">
         <v>2</v>
       </c>
@@ -8619,7 +8777,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
         <v>4</v>
       </c>
@@ -8711,7 +8868,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>眼鏡レンズ</t>
+        </is>
+      </c>
       <c r="H90" t="n">
         <v>3</v>
       </c>
@@ -8803,7 +8964,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>3</v>
       </c>
@@ -8895,7 +9055,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>4</v>
       </c>
@@ -8993,7 +9152,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H93" t="n">
         <v>4</v>
       </c>
@@ -9091,7 +9254,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>視覚の閾値</t>
+        </is>
+      </c>
       <c r="H94" t="n">
         <v>3</v>
       </c>
@@ -9183,7 +9350,11 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>単眼運動とその法則</t>
+        </is>
+      </c>
       <c r="H95" t="n">
         <v>2</v>
       </c>
@@ -9275,7 +9446,6 @@
           <t>脳、神経系疾患</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
         <v>2</v>
       </c>
@@ -9367,7 +9537,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H97" t="n">
         <v>4</v>
       </c>
@@ -9465,7 +9639,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>3</v>
       </c>
@@ -9563,7 +9736,6 @@
           <t>脳、神経系疾患</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>1</v>
       </c>
@@ -9655,7 +9827,11 @@
           <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>定義</t>
+        </is>
+      </c>
       <c r="H100" t="n">
         <v>2</v>
       </c>
@@ -9747,7 +9923,11 @@
           <t>瞳孔反応</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>対光反射</t>
+        </is>
+      </c>
       <c r="H101" t="n">
         <v>2</v>
       </c>
@@ -9839,7 +10019,6 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
         <v>1</v>
       </c>
@@ -9931,7 +10110,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>3</v>
       </c>
@@ -10023,7 +10201,11 @@
           <t>前眼部、透光体検査</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>細隙灯顕微鏡検査</t>
+        </is>
+      </c>
       <c r="H104" t="n">
         <v>3</v>
       </c>
@@ -10115,7 +10297,11 @@
           <t>瞳孔</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>瞳孔緊張症〈緊張性瞳孔〉</t>
+        </is>
+      </c>
       <c r="H105" t="n">
         <v>3</v>
       </c>
@@ -10207,7 +10393,6 @@
           <t>心臓、血管の構造と機能</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>3</v>
       </c>
@@ -10299,7 +10484,6 @@
           <t>隅角検査</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>3</v>
       </c>
@@ -10391,7 +10575,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H108" t="n">
         <v>3</v>
       </c>
@@ -10489,7 +10677,11 @@
           <t>眼鏡、コンタクトレンズ検査</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>コンタクトレンズ検査</t>
+        </is>
+      </c>
       <c r="H109" t="n">
         <v>3</v>
       </c>
@@ -10581,7 +10773,6 @@
           <t>公衆衛生総論</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>2</v>
       </c>
@@ -10673,7 +10864,6 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>1</v>
       </c>
@@ -10765,7 +10955,11 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>インシデント、アクシデントとレポート</t>
+        </is>
+      </c>
       <c r="H112" t="n">
         <v>1</v>
       </c>
@@ -10857,7 +11051,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
         <v>2</v>
       </c>
@@ -10949,7 +11142,11 @@
           <t>屈折検査</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>自覚的屈折検査</t>
+        </is>
+      </c>
       <c r="H114" t="n">
         <v>1</v>
       </c>
@@ -11041,7 +11238,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
         <v>3</v>
       </c>
@@ -11133,7 +11329,6 @@
           <t>網膜</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
         <v>2</v>
       </c>
@@ -11225,7 +11420,6 @@
           <t>硝子体</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
         <v>2</v>
       </c>
@@ -11317,7 +11511,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>視神経炎</t>
+        </is>
+      </c>
       <c r="H118" t="n">
         <v>3</v>
       </c>
@@ -11409,7 +11607,11 @@
           <t>ぶどう膜</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>ぶどう膜炎</t>
+        </is>
+      </c>
       <c r="H119" t="n">
         <v>2</v>
       </c>
@@ -11501,7 +11703,11 @@
           <t>硝子体</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>硝子体出血、混濁、後部硝子体剥離</t>
+        </is>
+      </c>
       <c r="H120" t="n">
         <v>2</v>
       </c>
@@ -11593,7 +11799,6 @@
           <t>中枢神経の構造と機能</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
         <v>2</v>
       </c>
@@ -11685,7 +11890,11 @@
           <t>緑内障</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>原発閉塞隅角緑内障</t>
+        </is>
+      </c>
       <c r="H122" t="n">
         <v>2</v>
       </c>
@@ -11777,7 +11986,11 @@
           <t>角膜</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>角膜変性（症）、角膜ジストロフィ</t>
+        </is>
+      </c>
       <c r="H123" t="n">
         <v>2</v>
       </c>
@@ -11869,7 +12082,11 @@
           <t>結膜</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>結膜炎</t>
+        </is>
+      </c>
       <c r="H124" t="n">
         <v>2</v>
       </c>
@@ -11961,7 +12178,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
         <v>2</v>
       </c>
@@ -12053,7 +12269,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H126" t="n">
         <v>4</v>
       </c>
@@ -12145,7 +12365,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>斜視特殊型</t>
+        </is>
+      </c>
       <c r="H127" t="n">
         <v>3</v>
       </c>
@@ -12237,7 +12461,6 @@
           <t>加齢、老化</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
         <v>3</v>
       </c>
@@ -12329,7 +12552,6 @@
           <t>定義</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
         <v>4</v>
       </c>
@@ -12421,7 +12643,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
         <v>3</v>
       </c>
@@ -12513,7 +12734,11 @@
           <t>屈折検査</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>自覚的屈折検査</t>
+        </is>
+      </c>
       <c r="H131" t="n">
         <v>3</v>
       </c>
@@ -12605,7 +12830,6 @@
           <t>定義</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
         <v>2</v>
       </c>
@@ -12697,7 +12921,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
         <v>2</v>
       </c>
@@ -12789,7 +13012,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>形態覚遮断弱視</t>
+        </is>
+      </c>
       <c r="H134" t="n">
         <v>3</v>
       </c>
@@ -12881,7 +13108,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
         <v>4</v>
       </c>
@@ -12973,7 +13199,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>遮閉法</t>
+        </is>
+      </c>
       <c r="H136" t="n">
         <v>3</v>
       </c>
@@ -13065,7 +13295,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>屈折矯正</t>
+        </is>
+      </c>
       <c r="H137" t="n">
         <v>3</v>
       </c>
@@ -13157,7 +13391,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H138" t="n">
         <v>4</v>
       </c>
@@ -13250,7 +13488,6 @@
           <t>脳、神経系疾患</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
         <v>3</v>
       </c>
@@ -13342,7 +13579,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
         <v>3</v>
       </c>
@@ -13434,7 +13670,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>屈折矯正</t>
+        </is>
+      </c>
       <c r="H141" t="n">
         <v>4</v>
       </c>
@@ -13526,7 +13766,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H142" t="n">
         <v>4</v>
       </c>
@@ -13619,7 +13863,11 @@
           <t>瞳孔</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>瞳孔緊張症〈緊張性瞳孔〉</t>
+        </is>
+      </c>
       <c r="H143" t="n">
         <v>3</v>
       </c>
@@ -13717,7 +13965,6 @@
           <t>眼位検査</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
         <v>4</v>
       </c>
@@ -13815,7 +14062,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
         <v>4</v>
       </c>
@@ -13908,7 +14154,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H146" t="n">
         <v>3</v>
       </c>
@@ -14006,7 +14256,6 @@
           <t>全身疾患と眼</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
         <v>3</v>
       </c>
@@ -14104,7 +14353,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
         <v>4</v>
       </c>
@@ -14202,7 +14450,11 @@
           <t>角膜</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>角膜変性（症）、角膜ジストロフィ</t>
+        </is>
+      </c>
       <c r="H149" t="n">
         <v>3</v>
       </c>
@@ -14300,7 +14552,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
         <v>3</v>
       </c>
@@ -14398,7 +14649,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H151" t="n">
         <v>5</v>
       </c>

--- a/CO国試data/CO_questions_2020.xlsx
+++ b/CO国試data/CO_questions_2020.xlsx
@@ -598,10 +598,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S2" t="b">
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -694,10 +692,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S3" t="b">
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -790,10 +786,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S4" t="b">
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -881,10 +875,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S5" t="b">
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -977,10 +969,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S6" t="b">
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1068,10 +1058,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S7" t="b">
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1159,10 +1147,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S8" t="b">
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1250,10 +1236,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S9" t="b">
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1341,10 +1325,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S10" t="b">
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1432,10 +1414,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S11" t="b">
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1523,10 +1503,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S12" t="b">
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1614,10 +1592,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S13" t="b">
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1710,10 +1686,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S14" t="b">
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1806,10 +1780,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S15" t="b">
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1897,10 +1869,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S16" t="b">
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1993,10 +1963,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S17" t="b">
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2089,10 +2057,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S18" t="b">
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2180,10 +2146,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S19" t="b">
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2276,10 +2240,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S20" t="b">
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2378,10 +2340,8 @@
           <t>2020_co_20_am020.jpg</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S21" t="b">
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2474,10 +2434,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S22" t="b">
+        <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2565,10 +2523,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S23" t="b">
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2656,10 +2612,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S24" t="b">
+        <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2752,10 +2706,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S25" t="b">
+        <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2843,10 +2795,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S26" t="b">
+        <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2939,10 +2889,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S27" t="b">
+        <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3030,10 +2978,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S28" t="b">
+        <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3126,10 +3072,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S29" t="b">
+        <v>0</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3314,10 +3258,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S31" t="b">
+        <v>0</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3506,10 +3448,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S33" t="b">
+        <v>0</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3689,10 +3629,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S35" t="b">
+        <v>0</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3877,10 +3815,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S37" t="b">
+        <v>0</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3968,10 +3904,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S38" t="b">
+        <v>0</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4064,10 +3998,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S39" t="b">
+        <v>0</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4160,10 +4092,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S40" t="b">
+        <v>0</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4256,10 +4186,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S41" t="b">
+        <v>0</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4352,10 +4280,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S42" t="b">
+        <v>0</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4539,10 +4465,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S44" t="b">
+        <v>0</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4630,10 +4554,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S45" t="b">
+        <v>0</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4822,10 +4744,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S47" t="b">
+        <v>0</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -4913,10 +4833,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S48" t="b">
+        <v>0</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5100,10 +5018,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S50" t="b">
+        <v>0</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5191,10 +5107,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S51" t="b">
+        <v>0</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5287,10 +5201,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S52" t="b">
+        <v>0</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5469,10 +5381,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S54" t="b">
+        <v>0</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5565,10 +5475,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S55" t="b">
+        <v>0</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5661,10 +5569,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S56" t="b">
+        <v>0</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5757,10 +5663,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S57" t="b">
+        <v>0</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5853,10 +5757,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S58" t="b">
+        <v>0</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6045,10 +5947,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S60" t="b">
+        <v>0</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6323,10 +6223,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S63" t="b">
+        <v>0</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6419,10 +6317,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S64" t="b">
+        <v>0</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6515,10 +6411,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S65" t="b">
+        <v>0</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6612,10 +6506,8 @@
           <t>2020_co_20_am065.jpg</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S66" t="b">
+        <v>0</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6709,10 +6601,8 @@
           <t>2020_co_20_am066.jpg</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S67" t="b">
+        <v>0</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -6806,10 +6696,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S68" t="b">
+        <v>0</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7010,10 +6898,8 @@
           <t>2020_co_20_am069.jpg</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S70" t="b">
+        <v>0</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7107,10 +6993,8 @@
           <t>2020_co_20_am070.jpg</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S71" t="b">
+        <v>0</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7209,10 +7093,8 @@
           <t>2020_co_20_am071.jpg</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S72" t="b">
+        <v>0</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7306,10 +7188,8 @@
           <t>2020_co_20_am072.jpg</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S73" t="b">
+        <v>0</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7403,10 +7283,8 @@
           <t>2020_co_20_am073.jpg</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S74" t="b">
+        <v>0</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7597,10 +7475,8 @@
           <t>2020_co_20_am075.jpg</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S76" t="b">
+        <v>0</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7693,10 +7569,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S77" t="b">
+        <v>0</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -7784,10 +7658,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S78" t="b">
+        <v>0</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -7880,10 +7752,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S79" t="b">
+        <v>0</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -7976,10 +7846,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S80" t="b">
+        <v>0</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8072,10 +7940,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S81" t="b">
+        <v>0</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8264,10 +8130,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S83" t="b">
+        <v>0</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8355,10 +8219,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S84" t="b">
+        <v>0</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8446,10 +8308,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S85" t="b">
+        <v>0</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8542,10 +8402,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S86" t="b">
+        <v>0</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -8638,10 +8496,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S87" t="b">
+        <v>0</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -8734,10 +8590,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S88" t="b">
+        <v>0</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -8825,10 +8679,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S89" t="b">
+        <v>0</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -8921,10 +8773,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S90" t="b">
+        <v>0</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9012,10 +8862,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S91" t="b">
+        <v>0</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9109,10 +8957,8 @@
           <t>2020_co_20_pm016.jpg</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S92" t="b">
+        <v>0</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9211,10 +9057,8 @@
           <t>2020_co_20_pm017.jpg</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S93" t="b">
+        <v>0</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9403,10 +9247,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S95" t="b">
+        <v>0</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9494,10 +9336,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S96" t="b">
+        <v>0</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -9693,10 +9533,8 @@
           <t>2020_co_20_pm022.jpg</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S98" t="b">
+        <v>0</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -9784,10 +9622,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S99" t="b">
+        <v>0</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -9880,10 +9716,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S100" t="b">
+        <v>0</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -9976,10 +9810,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S101" t="b">
+        <v>0</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10067,10 +9899,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S102" t="b">
+        <v>0</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10254,10 +10084,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S104" t="b">
+        <v>0</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10350,10 +10178,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S105" t="b">
+        <v>0</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10441,10 +10267,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S106" t="b">
+        <v>0</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10532,10 +10356,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S107" t="b">
+        <v>0</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -10634,10 +10456,8 @@
           <t>2020_co_20_pm032.jpg</t>
         </is>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S108" t="b">
+        <v>0</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -10730,10 +10550,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S109" t="b">
+        <v>0</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -10821,10 +10639,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S110" t="b">
+        <v>0</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -10912,10 +10728,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S111" t="b">
+        <v>0</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11008,10 +10822,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S112" t="b">
+        <v>0</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11099,10 +10911,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S113" t="b">
+        <v>0</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11195,10 +11005,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S114" t="b">
+        <v>0</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11286,10 +11094,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S115" t="b">
+        <v>0</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -11377,10 +11183,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S116" t="b">
+        <v>0</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -11847,10 +11651,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S121" t="b">
+        <v>0</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -11943,10 +11745,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S122" t="b">
+        <v>0</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -12135,10 +11935,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S124" t="b">
+        <v>0</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12226,10 +12024,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S125" t="b">
+        <v>0</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12418,10 +12214,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S127" t="b">
+        <v>0</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -12509,10 +12303,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S128" t="b">
+        <v>0</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -12691,10 +12483,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S130" t="b">
+        <v>0</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -12787,10 +12577,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S131" t="b">
+        <v>0</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -12969,10 +12757,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S133" t="b">
+        <v>0</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13065,10 +12851,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S134" t="b">
+        <v>0</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -13252,10 +13036,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S136" t="b">
+        <v>0</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -13348,10 +13130,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S137" t="b">
+        <v>0</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -13445,10 +13225,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S138" t="b">
+        <v>0</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -13536,10 +13314,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S139" t="b">
+        <v>0</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -13723,10 +13499,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S141" t="b">
+        <v>0</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -13820,10 +13594,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S142" t="b">
+        <v>0</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -13922,10 +13694,8 @@
           <t>2020_co_20_pm067.jpg</t>
         </is>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S143" t="b">
+        <v>0</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -14019,10 +13789,8 @@
           <t>2020_co_20_pm068.jpg</t>
         </is>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S144" t="b">
+        <v>0</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -14213,10 +13981,8 @@
           <t>2020_co_20_pm070.jpg</t>
         </is>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S146" t="b">
+        <v>0</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -14310,10 +14076,8 @@
           <t>2020_co_20_pm071.jpg</t>
         </is>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S147" t="b">
+        <v>0</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -14407,10 +14171,8 @@
           <t>2020_co_20_pm072.jpg</t>
         </is>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S148" t="b">
+        <v>0</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -14509,10 +14271,8 @@
           <t>2020_co_20_pm073.jpg</t>
         </is>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S149" t="b">
+        <v>0</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -14606,10 +14366,8 @@
           <t>2020_co_20_pm074.jpg</t>
         </is>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S150" t="b">
+        <v>0</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -14708,10 +14466,8 @@
           <t>2020_co_20_pm075.jpg</t>
         </is>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S151" t="b">
+        <v>0</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>

--- a/CO国試data/CO_questions_2020.xlsx
+++ b/CO国試data/CO_questions_2020.xlsx
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3161,10 +3161,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S30" t="b">
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3339,7 +3337,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3352,10 +3350,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S32" t="b">
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3524,7 +3520,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3537,10 +3533,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S34" t="b">
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3706,7 +3700,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3719,10 +3713,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S36" t="b">
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4361,7 +4353,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4374,10 +4366,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S43" t="b">
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4635,7 +4625,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4648,10 +4638,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S46" t="b">
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -4914,7 +4902,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4927,10 +4915,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S49" t="b">
+        <v>1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5277,7 +5263,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5290,10 +5276,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S53" t="b">
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5838,7 +5822,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5851,10 +5835,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S59" t="b">
+        <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6028,7 +6010,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6041,10 +6023,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S61" t="b">
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6119,7 +6099,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6132,10 +6112,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S62" t="b">
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6778,7 +6756,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -6796,10 +6774,8 @@
           <t>2020_co_20_am068.jpg</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S69" t="b">
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7365,7 +7341,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -7378,10 +7354,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S75" t="b">
+        <v>1</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8021,7 +7995,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -8034,10 +8008,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S82" t="b">
+        <v>1</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9138,7 +9110,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -9151,10 +9123,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S94" t="b">
+        <v>1</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9418,7 +9388,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -9436,10 +9406,8 @@
           <t>2020_co_20_pm021.jpg;2020_co_20_pm021_2.jpg;2020_co_20_pm021_3.jpg;2020_co_20_pm021_4.jpg;2020_co_20_pm021_5.jpg</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S97" t="b">
+        <v>1</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -9975,7 +9943,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -9988,10 +9956,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S103" t="b">
+        <v>1</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10343,7 +10309,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -10357,7 +10323,7 @@
         </is>
       </c>
       <c r="S107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11081,7 +11047,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>ABCDE</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -11095,7 +11061,7 @@
         </is>
       </c>
       <c r="S115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -11259,7 +11225,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -11272,10 +11238,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S117" t="b">
+        <v>1</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -11355,7 +11319,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -11368,10 +11332,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S118" t="b">
+        <v>1</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -11451,7 +11413,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -11464,10 +11426,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S119" t="b">
+        <v>1</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -11547,7 +11507,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -11560,10 +11520,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S120" t="b">
+        <v>1</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -11826,7 +11784,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -11839,10 +11797,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S123" t="b">
+        <v>1</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -12105,7 +12061,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -12118,10 +12074,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S126" t="b">
+        <v>1</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -12379,7 +12333,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -12392,10 +12346,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S129" t="b">
+        <v>1</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -12653,7 +12605,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -12666,10 +12618,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S132" t="b">
+        <v>1</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -12927,7 +12877,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -12940,10 +12890,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S135" t="b">
+        <v>1</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -13390,7 +13338,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -13403,10 +13351,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S140" t="b">
+        <v>1</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -13866,7 +13812,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -13879,10 +13825,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S145" t="b">
+        <v>1</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
